--- a/data.xlsx
+++ b/data.xlsx
@@ -1020,12 +1020,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Analog media (cassette, VHS) preservation, digital format conversion, and vintage audio-visual device restoration.</t>
+          <t>সোশ্যাল মিডিয়া কার্যক্রম এবং কন্টেন্ট</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>অ্যানালগ মিডিয়া (ক্যাসেট, ভিএইচএস) সংরক্ষণ, ডিজিটাল ফরমেটে রূপান্তর এবং ভিন্টেজ অডিও-ভিজ্যুয়াল ডিভাইস পুনরুদ্ধার কার্যক্রম।</t>
+          <t>Social media activities and content.</t>
         </is>
       </c>
     </row>
@@ -1037,12 +1037,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Media Archiving</t>
+          <t>মিডিয়া</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>মিডিয়া আর্কাইভ</t>
+          <t>Media</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Vintage Media Digitization</t>
+          <t>সোশ্যাল মিডিয়া কার্যক্রম</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ভিন্টেজ মিডিয়া ডিজিটালাইজেশন</t>
+          <t>Social Media Activities</t>
         </is>
       </c>
     </row>
@@ -2601,9 +2601,6 @@
           <t>লেখক: মো. মুকিদ হাসান সিয়াম</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2634,8 +2631,6 @@
           <t>ভূমিকা</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>ধর্ম মানুষের অন্তরের বিষয়। কিন্তু যখন তা লোকদেখানো প্রতিযোগিতায় পরিণত হয়, তখনই সমাজে তৈরি হয় চরম অরাজকতা ও হিপোক্রিসি।</t>
@@ -2681,8 +2676,6 @@
           <t>অধ্যায় ১: সস্তা আবেগ</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>ফুটবল একটি নিছক বিনোদন। কিন্তু এখানেও কিছু মানুষ ধর্মের কার্ড খেলে বলেন, "মুসলিম দেশ হিসেবে অমুক দলকে সাপোর্ট করতে হবে।"</t>
@@ -2728,8 +2721,6 @@
           <t>অধ্যায় ২: আলেমদের প্রতিযোগিতা</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>একসময় মানুষ খুতবা শুনতে মসজিদে যেত আত্মশুদ্ধির জন্য। আর এখন? অনেকেই ইউটিউবে নেমেছেন ভিউ বাড়ানোর অসুস্থ প্রতিযোগিতায়।</t>
@@ -2775,8 +2766,6 @@
           <t>অধ্যায় ৩: বাণিজ্যিকীকরণ</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>ধর্ম প্রচারের নামে এখন চলছে জাঁকজমকপূর্ণ ব্যবসা। চমৎকার মিউজিক আর বলিউডি সুরের সাথে মিল রেখে তৈরি হচ্ছে ইসলামিক গজল।</t>
@@ -2822,8 +2811,6 @@
           <t>অধ্যায় ৪: ১৪০০ বছরের ইতিহাস</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>যারা বড় বড় ফতোয়া দেন, তারা অমুসলিমদের তৈরি করা ফেসবুক আর ইউটিউব ব্যবহার করেই ইসলাম রক্ষার বড়াই করেন।</t>
@@ -2869,8 +2856,6 @@
           <t>উপসংহার</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>আমি নিজেকে নিখুঁত কোনো ঈমানদার দাবি করি না। কিন্তু আমি এই ধর্মের একজন অংশ। তাই যখন দেখি ধর্মের নামে ব্যবসা ও ক্ষমতার অপব্যবহার চলছে, তখন তা চরম বিরক্তির কারণ হয়ে দাঁড়ায়।</t>
@@ -2916,11 +2901,6 @@
           <t>সমাপ্ত</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2961,9 +2941,6 @@
           <t>Author: Md. Mukid Hasan Seiam</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2994,8 +2971,6 @@
           <t>Preface</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>Religion is a matter of the heart. However, when it transforms into a showy competition, it breeds chaos and hypocrisy within society.</t>
@@ -3041,8 +3016,6 @@
           <t>Chapter 1: Cheap Emotions</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>Football is merely a form of entertainment. Yet, even here, some people play the religious card, insisting, "As a Muslim country, we must support such-and-such team."</t>
@@ -3088,8 +3061,6 @@
           <t>Chapter 2: The Clerics' Race</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>Once, people visited mosques to listen to sermons for spiritual purification. Today, many have entered an unhealthy online race to boost YouTube views.</t>
@@ -3135,8 +3106,6 @@
           <t>Chapter 3: Commercialization</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>Under the banner of preaching, a glamorous business is thriving. Islamic ghazals are now composed in tune with Bollywood beats and melodies.</t>
@@ -3182,8 +3151,6 @@
           <t>Chapter 4: 1400 Years of History</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>Those who issue grand fatwas boast of defending Islam while utilizing Facebook and YouTube—platforms created by non-Muslims—to spread their message.</t>
@@ -3229,8 +3196,6 @@
           <t>Conclusion</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>I do not claim to be a perfect believer, but I am a part of this faith. Thus, when I witness business and abuse of power running rampant in the name of religion, it becomes a source of extreme frustration.</t>
@@ -3276,11 +3241,6 @@
           <t>The End</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3321,9 +3281,6 @@
           <t>লেখক: মো. মুকিদ হাসান সিয়াম</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3354,8 +3311,6 @@
           <t>ভূমিকা</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>বাইরে থেকে কর্পোরেট জগৎকে ক্যারিয়ার গড়ার চূড়ান্ত গন্তব্য মনে হলেও, এটি অনেক সময়ই একটি সুকৌশলী ফাঁদ। আমরা আসলে স্বাধীন মানুষ, নাকি আধুনিক মজুরি-দাসের প্রথায় জড়িয়ে পড়েছি?</t>
@@ -3401,8 +3356,6 @@
           <t>১. আধুনিক মজুরি-দাসত্ব</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>কর্পোরেট দুনিয়া শুধু সার্ভিস কেনে না; তারা আপনার পুরো 'সময়', মানসিকতা এবং শর্তহীন আনুগত্য কিনে নিতে চায়। যখনই স্কিল বিক্রির সীমা পেরিয়ে দাসত্ব আশা করা হয়, তখনই এটি খাঁচা মনে হতে শুরু করে।</t>
@@ -3448,8 +3401,6 @@
           <t>২. পদবির মোহ ও স্কিলের মৃত্যু</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
           <t>প্রমোশন দিতে দিতে এমন একটি পদে নিয়ে যাওয়া হয়, যে কাজের জন্য সে সম্পূর্ণ অযোগ্য। পদবির পেছনে ছুটতে গিয়ে কোর স্কিলগুলো চর্চার অভাবে জঞ্জালে পরিণত হয়।</t>
@@ -3495,8 +3446,6 @@
           <t>৩. সেরা ট্রেনিং গ্রাউন্ড</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>এত ফাঁদ জেনেও চাকরি করার প্রেরণা কী? স্বাধীন উদ্যোগ গড়ার আগে এই ফাঁদে পা দেওয়াটাই বড় বুদ্ধিমত্তার কাজ: বাবার অঢেল টাকা থাকলেও অন্যের অধীনে কাজ করলে টাকার প্রকৃত মূল্য এবং ভেতরের ইগো ভেঙে ফেলা শেখা যায়।</t>
@@ -3542,8 +3491,6 @@
           <t>৪. কর্পোরেট কাদের জন্য?</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>এই সিস্টেমটিতে মূলত দুধরনের মানুষ লাভবান হয়: ১. দ্য ট্রিকস্টারস বা ধূর্ত মানুষ, এবং ২. টাইম-টার্গেট লার্নার যারা শুধু কাজ ও অভিজ্ঞতা শিখতে আসে।</t>
@@ -3589,8 +3536,6 @@
           <t>৫. ইসলাম কেন টার্গেট হয়?</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>কর্পোরেট চায় শ্রমবাজারে কর্মীর সংখ্যা দ্বিগুণ করতে। ইসলাম পরিবারকে হেডকোয়ার্টার্স ধরে চমৎকার দায়িত্ব ভাগ করেছে—পুরুষ ফিল্ড এজেন্ট, নারী ইনডোর এক্সিকিউটিভ।</t>
@@ -3636,8 +3581,6 @@
           <t>৬. ভোগবাদ ও ঋণের ফাঁদ</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>কর্পোরেট পুঁজিবাদের বড় হাতিয়ার মানুষকে ঋণের (লোন, ক্রেডিট কার্ড) জালে আটকে ফেলা। ইসলামে সুদ হারাম এবং অপচয় কঠোরভাবে নিষিদ্ধ।</t>
@@ -3683,8 +3626,6 @@
           <t>শেষ কথা</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>কর্পোরেট জগৎ কাজের অভিজ্ঞতা নেওয়ার জন্য দারুণ জায়গা, কিন্তু এটি কখনোই স্বাধীন জীবনের চূড়ান্ত গন্তব্য হতে পারে না। যে এই সত্যটা বুঝতে পারে, সে ফাঁদ এড়িয়ে নিজের রাস্তা নিজেই তৈরি করে নেয়।</t>
@@ -3730,11 +3671,6 @@
           <t>সমাপ্ত</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3775,9 +3711,6 @@
           <t>Author: Md. Mukid Hasan Seiam</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3808,8 +3741,6 @@
           <t>Preface</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>While the corporate world seems like the ultimate destination for career growth from the outside, from the inside it is often a clever trap. Are we working as free individuals or getting entangled in modern wage-slavery?</t>
@@ -3855,8 +3786,6 @@
           <t>Chapter 1: Modern Wage-Slavery</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
           <t>The corporate world does not just buy a service; it wants to buy your entire time, mindset, and unconditional loyalty. When it demands slavery beyond services, it feels like a cage.</t>
@@ -3902,8 +3831,6 @@
           <t>Chapter 2: Job Titles &amp; Skill Death</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
           <t>People are promoted until they reach a level of incompetence. In the pursuit of titles, core skills decay into garbage information due to a lack of practice.</t>
@@ -3949,8 +3876,6 @@
           <t>Chapter 3: Best Training Ground</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
           <t>Why work a job despite these traps? Working under others teaches you the real value of money and breaks your ego. It provides networking and builds tolerance.</t>
@@ -3996,8 +3921,6 @@
           <t>Chapter 4: Who is Corporate For?</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
           <t>Two types of people benefit in this system: 1. The Tricksters who navigate the system cunningly, and 2. Time-Target Learners who only come to learn and gain experience.</t>
@@ -4043,8 +3966,6 @@
           <t>Chapter 5: Why is Islam Targeted?</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
           <t>Corporates want to double the labor market. Islam defines the family as society's headquarters, delegating the male as the field agent and the female as the indoor manager.</t>
@@ -4090,8 +4011,6 @@
           <t>Chapter 6: Consumerism &amp; Debt</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
           <t>The biggest weapon of corporate capitalism is trapping people in debt. Islam strictly forbids interest (usury) and wastefulness, which makes it a target.</t>
@@ -4137,8 +4056,6 @@
           <t>Conclusion</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
           <t>The corporate world is a great place to gain experience, but it can never be the ultimate destination of a free life. He who understands this truth escapes the trap and carves his own path.</t>
@@ -4184,11 +4101,6 @@
           <t>The End</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -1020,12 +1020,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
+          <t>Social media activities and content.</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
           <t>সোশ্যাল মিডিয়া কার্যক্রম এবং কন্টেন্ট</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Social media activities and content.</t>
         </is>
       </c>
     </row>
@@ -1037,12 +1037,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
           <t>মিডিয়া</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Media</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
+          <t>Social Media Activities</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
           <t>সোশ্যাল মিডিয়া কার্যক্রম</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Social Media Activities</t>
         </is>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -1462,7 +1462,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>I am M. Mukid Hasan Seiam. With over 8 years in tech diagnostics, I solve complex problems and am currently exploring the world of open-source game development.</t>
+          <t>With over 8 years in tech diagnostics, I solve and learn complex problems and i am currently exploring the world of open-source softwares,  2d games  development via a.i. tools.</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">

--- a/data.xlsx
+++ b/data.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C122"/>
+  <dimension ref="A1:C123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2488,6 +2488,23 @@
       <c r="C122" t="inlineStr">
         <is>
           <t>শেলফে পিডিএফ আপলোড করুন</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>hero_name</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>ukid Hasan Seiam</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>মুকিদ হাসান সিয়াম</t>
         </is>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -1460,11 +1460,7 @@
           <t>hero_desc</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>With over 8 years in tech diagnostics, I solve and learn complex problems and i am currently exploring the world of open-source softwares,  2d games  development via a.i. tools.</t>
-        </is>
-      </c>
+      <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr">
         <is>
           <t>আমি মো. মুকিদ হাসান সিয়াম। টেক ডায়াগনস্টিক্সে ৮ বছরেরও বেশি সময় ধরে জটিল সমস্যার সমাধান করছি এবং বর্তমানে ওপেন-সোর্স গেম ডেভেলপমেন্টের জগৎ নিয়ে কাজ করছি।</t>
